--- a/AAII_Financials/Quarterly/LSF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LSF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
   <si>
     <t>LSF</t>
   </si>
@@ -656,428 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F8" s="3">
         <v>13300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>12900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>12000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>11700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>11600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>11800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>10000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>9900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>9200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>7700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>9000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>9300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>10900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>9200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>7400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>7100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>7600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>5600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>5500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>3000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F9" s="3">
         <v>8800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>8200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>7200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>6800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>7100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>5800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>5900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>5500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>6300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>5800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>9400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>6800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>7100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>7400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>7200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>7700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>7000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>5600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>5800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>5700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>4300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>3400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F10" s="3">
         <v>4500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>4800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>4900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>4500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1900</v>
-      </c>
-      <c r="T10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>3200</v>
       </c>
       <c r="V10" s="3">
         <v>2200</v>
       </c>
       <c r="W10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="X10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1800</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>1900</v>
       </c>
       <c r="Z10" s="3">
         <v>1300</v>
       </c>
       <c r="AA10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC10" s="3">
         <v>2100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,32 +1137,34 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>10</v>
       </c>
@@ -1152,11 +1180,11 @@
       <c r="O12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P12" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
+      <c r="P12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R12" s="3">
         <v>100</v>
@@ -1165,25 +1193,25 @@
         <v>100</v>
       </c>
       <c r="T12" s="3">
+        <v>100</v>
+      </c>
+      <c r="U12" s="3">
+        <v>100</v>
+      </c>
+      <c r="V12" s="3">
         <v>200</v>
-      </c>
-      <c r="U12" s="3">
-        <v>200</v>
-      </c>
-      <c r="V12" s="3">
-        <v>400</v>
       </c>
       <c r="W12" s="3">
         <v>200</v>
       </c>
       <c r="X12" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z12" s="3">
         <v>300</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>100</v>
       </c>
       <c r="AA12" s="3">
         <v>100</v>
@@ -1195,10 +1223,10 @@
         <v>100</v>
       </c>
       <c r="AD12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF12" s="3">
         <v>0</v>
@@ -1206,8 +1234,14 @@
       <c r="AG12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,23 +1335,29 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3">
         <v>-700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1342,70 +1382,76 @@
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3">
         <v>9900</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>8000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>200</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1438,10 +1484,10 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1491,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F17" s="3">
         <v>15800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>13200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>12400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>11900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>12100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>12000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>10300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>9200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>12000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>11400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>12400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>24600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>14700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>13600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>23300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>16400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>16200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>15500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>12800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>11600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>11000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>8600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>7500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>6400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>5900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>5300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>4300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>6000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>-2800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-4900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-14000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-7000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-6300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-5400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,13 +1814,15 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1763,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>-100</v>
@@ -1787,26 +1855,26 @@
         <v>-100</v>
       </c>
       <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1841,24 +1909,30 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-200</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-100</v>
       </c>
       <c r="H21" s="3">
         <v>-300</v>
@@ -1867,79 +1941,85 @@
         <v>-100</v>
       </c>
       <c r="J21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-4000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-5500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-4600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-13800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-6700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-5000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-6000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-5200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1979,11 +2059,11 @@
       <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2033,8 +2113,14 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2042,94 +2128,100 @@
         <v>-1800</v>
       </c>
       <c r="E23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G23" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-100</v>
       </c>
       <c r="H23" s="3">
         <v>-400</v>
       </c>
       <c r="I23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-5700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-14100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-7000</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-6300</v>
       </c>
       <c r="W23" s="3">
         <v>-5300</v>
       </c>
       <c r="X23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2137,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-4700</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -2160,36 +2252,36 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>10</v>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>10</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -2202,14 +2294,14 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>10</v>
+      <c r="AA24" s="3">
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
+      <c r="AC24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -2223,8 +2315,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,8 +2416,14 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2327,13 +2431,13 @@
         <v>-1800</v>
       </c>
       <c r="E26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G26" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-200</v>
       </c>
       <c r="H26" s="3">
         <v>-400</v>
@@ -2342,93 +2446,99 @@
         <v>-200</v>
       </c>
       <c r="J26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-5700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-4900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-14100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-6900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-5400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-6300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-5300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-200</v>
       </c>
       <c r="H27" s="3">
         <v>-400</v>
@@ -2437,79 +2547,85 @@
         <v>-200</v>
       </c>
       <c r="J27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-5700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-14100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-6900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-5400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-6300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-5300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>5300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,13 +3022,19 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2903,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>100</v>
@@ -2927,26 +3067,26 @@
         <v>100</v>
       </c>
       <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2981,10 +3121,16 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2992,13 +3138,13 @@
         <v>-1800</v>
       </c>
       <c r="E33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-200</v>
       </c>
       <c r="H33" s="3">
         <v>-400</v>
@@ -3007,79 +3153,85 @@
         <v>-200</v>
       </c>
       <c r="J33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-5700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-14100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-6900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-5400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-6300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-5300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>5300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,8 +3325,14 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3182,13 +3340,13 @@
         <v>-1800</v>
       </c>
       <c r="E35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-200</v>
       </c>
       <c r="H35" s="3">
         <v>-400</v>
@@ -3197,179 +3355,191 @@
         <v>-200</v>
       </c>
       <c r="J35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-5700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-14100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-6900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-5400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-6300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-5300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>5300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,34 +3610,36 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F41" s="3">
         <v>5100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K41" s="3">
-        <v>7100</v>
       </c>
       <c r="L41" s="3">
         <v>7600</v>
@@ -3474,50 +3648,50 @@
         <v>7100</v>
       </c>
       <c r="N41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="O41" s="3">
+        <v>7100</v>
+      </c>
+      <c r="P41" s="3">
         <v>10500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>11800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>17700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>20900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>24400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>27200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>22900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>30900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>34700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>51500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>57200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>72900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>8500</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3533,25 +3707,31 @@
       <c r="AG41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>300</v>
-      </c>
-      <c r="G42" s="3">
-        <v>200</v>
-      </c>
-      <c r="H42" s="3">
-        <v>200</v>
       </c>
       <c r="I42" s="3">
         <v>200</v>
@@ -3572,14 +3752,14 @@
         <v>200</v>
       </c>
       <c r="O42" s="3">
+        <v>200</v>
+      </c>
+      <c r="P42" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3587,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
         <v>8600</v>
-      </c>
-      <c r="U42" s="3">
-        <v>8700</v>
-      </c>
-      <c r="V42" s="3">
-        <v>8700</v>
       </c>
       <c r="W42" s="3">
         <v>8700</v>
@@ -3602,17 +3782,17 @@
         <v>8700</v>
       </c>
       <c r="Y42" s="3">
+        <v>8700</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>8700</v>
+      </c>
+      <c r="AA42" s="3">
         <v>500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>4500</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3628,86 +3808,92 @@
       <c r="AG42" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI42" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F43" s="3">
         <v>3900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>1600</v>
-      </c>
-      <c r="R43" s="3">
-        <v>1300</v>
       </c>
       <c r="S43" s="3">
         <v>1600</v>
       </c>
       <c r="T43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V43" s="3">
         <v>1900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1100</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3723,86 +3909,92 @@
       <c r="AG43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>17300</v>
+      </c>
+      <c r="F44" s="3">
         <v>8300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>10100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>11200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>9900</v>
-      </c>
-      <c r="H44" s="3">
-        <v>6800</v>
-      </c>
-      <c r="I44" s="3">
-        <v>6500</v>
       </c>
       <c r="J44" s="3">
         <v>6800</v>
       </c>
       <c r="K44" s="3">
-        <v>5900</v>
+        <v>6500</v>
       </c>
       <c r="L44" s="3">
         <v>6800</v>
       </c>
       <c r="M44" s="3">
+        <v>5900</v>
+      </c>
+      <c r="N44" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O44" s="3">
         <v>7000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>6100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>8800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>8700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>9900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>10200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>10300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>10800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>7700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>6300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3500</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>10</v>
       </c>
@@ -3818,86 +4010,92 @@
       <c r="AG44" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI44" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
       </c>
       <c r="H45" s="3">
         <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
       </c>
       <c r="K45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L45" s="3">
         <v>100</v>
       </c>
       <c r="M45" s="3">
+        <v>100</v>
+      </c>
+      <c r="N45" s="3">
+        <v>100</v>
+      </c>
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>3100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>3100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3913,86 +4111,92 @@
       <c r="AG45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>37500</v>
+      </c>
+      <c r="F46" s="3">
         <v>18800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>18400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>19200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>20200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>18000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>17300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>16500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>16100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>16300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>19900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>22900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>27500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>33300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>37300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>41700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>47700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>53400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>57800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>72300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>76000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>80400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>18400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>10</v>
       </c>
@@ -4008,8 +4212,14 @@
       <c r="AG46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4049,11 +4259,11 @@
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4103,22 +4313,28 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>600</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>300</v>
       </c>
       <c r="H48" s="3">
         <v>300</v>
@@ -4127,62 +4343,62 @@
         <v>300</v>
       </c>
       <c r="J48" s="3">
+        <v>300</v>
+      </c>
+      <c r="K48" s="3">
+        <v>300</v>
+      </c>
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>11200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>11700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>11900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>4500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>4100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>3800</v>
-      </c>
-      <c r="W48" s="3">
-        <v>3500</v>
-      </c>
-      <c r="X48" s="3">
-        <v>3500</v>
       </c>
       <c r="Y48" s="3">
         <v>3500</v>
       </c>
       <c r="Z48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AB48" s="3">
         <v>3000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>10</v>
       </c>
@@ -4198,73 +4414,79 @@
       <c r="AG48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>36800</v>
+      </c>
+      <c r="F49" s="3">
         <v>200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>11300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>11500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>11600</v>
-      </c>
-      <c r="W49" s="3">
-        <v>100</v>
-      </c>
-      <c r="X49" s="3">
-        <v>100</v>
       </c>
       <c r="Y49" s="3">
         <v>100</v>
@@ -4272,11 +4494,11 @@
       <c r="Z49" s="3">
         <v>100</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>10</v>
+      <c r="AA49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>100</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>10</v>
@@ -4293,8 +4515,14 @@
       <c r="AG49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4717,14 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4524,45 +4764,45 @@
       <c r="O52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>10</v>
+      <c r="P52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U52" s="3">
         <v>900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>10</v>
       </c>
@@ -4578,8 +4818,14 @@
       <c r="AG52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,86 +4919,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>145700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>74900</v>
+      </c>
+      <c r="F54" s="3">
         <v>19200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>18900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>20400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>21500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>19300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>18800</v>
-      </c>
-      <c r="J54" s="3">
-        <v>18000</v>
-      </c>
-      <c r="K54" s="3">
-        <v>17600</v>
       </c>
       <c r="L54" s="3">
         <v>18000</v>
       </c>
       <c r="M54" s="3">
+        <v>17600</v>
+      </c>
+      <c r="N54" s="3">
+        <v>18000</v>
+      </c>
+      <c r="O54" s="3">
         <v>19400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>21800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>25000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>30000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>47600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>52200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>57700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>65800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>71400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>75700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>78600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>82300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>86700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>24700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>10</v>
       </c>
@@ -4768,8 +5020,14 @@
       <c r="AG54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,85 +5098,87 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1900</v>
       </c>
       <c r="K57" s="3">
         <v>1700</v>
       </c>
       <c r="L57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
-      </c>
-      <c r="X57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>2300</v>
       </c>
       <c r="Z57" s="3">
         <v>1300</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>10</v>
+      <c r="AA57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>1300</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>10</v>
@@ -4933,16 +5195,22 @@
       <c r="AG57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
@@ -4975,10 +5243,10 @@
         <v>100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5028,13 +5296,19 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>10</v>
+      <c r="D59" s="3">
+        <v>4100</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>10</v>
@@ -5048,66 +5322,66 @@
       <c r="H59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>700</v>
       </c>
       <c r="N59" s="3">
         <v>400</v>
       </c>
       <c r="O59" s="3">
+        <v>700</v>
+      </c>
+      <c r="P59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>4400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>10</v>
       </c>
@@ -5123,86 +5397,92 @@
       <c r="AG59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F60" s="3">
         <v>7700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>8000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4400</v>
-      </c>
-      <c r="M60" s="3">
-        <v>6100</v>
-      </c>
-      <c r="N60" s="3">
-        <v>6200</v>
       </c>
       <c r="O60" s="3">
         <v>6100</v>
       </c>
       <c r="P60" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>6100</v>
+      </c>
+      <c r="R60" s="3">
         <v>7500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>5000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3800</v>
-      </c>
-      <c r="U60" s="3">
-        <v>3500</v>
-      </c>
-      <c r="V60" s="3">
-        <v>3700</v>
       </c>
       <c r="W60" s="3">
         <v>3500</v>
       </c>
       <c r="X60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Z60" s="3">
         <v>2700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2400</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>10</v>
       </c>
@@ -5218,19 +5498,25 @@
       <c r="AG60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
@@ -5239,10 +5525,10 @@
         <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>200</v>
@@ -5251,19 +5537,19 @@
         <v>200</v>
       </c>
       <c r="M61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O61" s="3">
         <v>300</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -5275,10 +5561,10 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>100</v>
@@ -5293,10 +5579,10 @@
         <v>100</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -5313,8 +5599,14 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5354,32 +5646,32 @@
       <c r="O62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4400</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>10</v>
+      <c r="X62" s="3">
+        <v>0</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>10</v>
@@ -5390,11 +5682,11 @@
       <c r="AA62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5408,8 +5700,14 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,86 +6003,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F66" s="3">
         <v>7800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>8200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4600</v>
-      </c>
-      <c r="M66" s="3">
-        <v>6400</v>
-      </c>
-      <c r="N66" s="3">
-        <v>6500</v>
       </c>
       <c r="O66" s="3">
         <v>6400</v>
       </c>
       <c r="P66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>6400</v>
+      </c>
+      <c r="R66" s="3">
         <v>7500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>9800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>9700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>4000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2500</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>10</v>
       </c>
@@ -5788,8 +6104,14 @@
       <c r="AG66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,16 +6343,22 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>110200</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>49300</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -6085,14 +6421,14 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>15900</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -6108,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,8 +6545,14 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6215,74 +6563,74 @@
         <v>-109600</v>
       </c>
       <c r="F72" s="3">
+        <v>-111400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-109600</v>
+      </c>
+      <c r="H72" s="3">
         <v>-108600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-108300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-108100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-107700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-107600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-107300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-106300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-106400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-103800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-100300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-96100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-80600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-74800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-69900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-55800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-48900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-43600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-37300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-31900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-27400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-24100</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>10</v>
       </c>
@@ -6298,8 +6646,14 @@
       <c r="AG72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,86 +6949,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F76" s="3">
         <v>11500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>12800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>13400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>13300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>13200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>13100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>12600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>12700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>13000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>18500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>22500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>37700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>43000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>48000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>62100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>67700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>71900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>75100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>79500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>82800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>6300</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>10</v>
       </c>
@@ -6678,8 +7050,14 @@
       <c r="AG76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,108 +7151,120 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6882,13 +7272,13 @@
         <v>-1800</v>
       </c>
       <c r="E81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-200</v>
       </c>
       <c r="H81" s="3">
         <v>-400</v>
@@ -6897,79 +7287,85 @@
         <v>-200</v>
       </c>
       <c r="J81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-5700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-14100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-6900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-5400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-6300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-5300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>5300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7399,10 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7033,13 +7431,13 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
@@ -7066,19 +7464,19 @@
         <v>300</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>10</v>
+      <c r="Z83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>100</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>10</v>
@@ -7092,14 +7490,20 @@
       <c r="AE83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,83 +8001,89 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F89" s="3">
         <v>100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3200</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-3900</v>
       </c>
       <c r="S89" s="3">
         <v>-3600</v>
       </c>
       <c r="T89" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="U89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V89" s="3">
         <v>-7900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-3300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-5800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-5100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>10</v>
       </c>
@@ -7662,14 +8096,20 @@
       <c r="AE89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,83 +8143,85 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>10</v>
+      <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-500</v>
+      <c r="P91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R91" s="3">
         <v>-500</v>
       </c>
       <c r="S91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U91" s="3">
         <v>-400</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-500</v>
       </c>
       <c r="V91" s="3">
         <v>-400</v>
       </c>
       <c r="W91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-600</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>10</v>
       </c>
@@ -7792,14 +8234,20 @@
       <c r="AE91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,83 +8442,89 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-48700</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-40200</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>10</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3">
-        <v>100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N94" s="3">
         <v>100</v>
       </c>
       <c r="O94" s="3">
+        <v>300</v>
+      </c>
+      <c r="P94" s="3">
         <v>100</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
       </c>
       <c r="Q94" s="3">
         <v>100</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>100</v>
+      </c>
+      <c r="T94" s="3">
         <v>1100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>7800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-11300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>3800</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>10</v>
       </c>
@@ -8077,14 +8537,20 @@
       <c r="AE94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8159,11 +8627,11 @@
       <c r="O96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8213,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,38 +8984,44 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>59900</v>
       </c>
       <c r="E100" s="3">
+        <v>49200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -8546,35 +9038,35 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>63100</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>10</v>
       </c>
@@ -8587,14 +9079,20 @@
       <c r="AE100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8634,11 +9132,11 @@
       <c r="O101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8688,83 +9186,89 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="E102" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-5900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-3500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>4200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-8000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-3800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-16900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-5500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-15700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>64400</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>10</v>
       </c>
@@ -8777,10 +9281,16 @@
       <c r="AE102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
